--- a/data/Electricity.xlsx
+++ b/data/Electricity.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/samarthg/Documents/invoiceAgent/invoiceEditor/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC5E8B9B-7666-1A44-949C-3212F989A9D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D08C246-42C5-4446-BEF5-7C836D0D9AB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="15980" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="15980" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="April" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="22">
   <si>
     <t>Customer Name</t>
   </si>
@@ -79,6 +79,15 @@
   </si>
   <si>
     <t>Invoiced</t>
+  </si>
+  <si>
+    <t>CGST</t>
+  </si>
+  <si>
+    <t>SGST</t>
+  </si>
+  <si>
+    <t>Grand Total</t>
   </si>
 </sst>
 </file>
@@ -97,6 +106,7 @@
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
@@ -156,7 +166,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
@@ -540,7 +550,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:H4"/>
+  <dimension ref="A1:H9"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.2">
@@ -642,6 +652,38 @@
       </c>
       <c r="H4" t="s">
         <v>11</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="G6" t="s">
+        <v>5</v>
+      </c>
+      <c r="H6">
+        <v>100.67</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="G7" t="s">
+        <v>19</v>
+      </c>
+      <c r="H7">
+        <v>9.06</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="G8" t="s">
+        <v>20</v>
+      </c>
+      <c r="H8">
+        <v>9.06</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="G9" t="s">
+        <v>21</v>
+      </c>
+      <c r="H9">
+        <v>118.79</v>
       </c>
     </row>
   </sheetData>
